--- a/Client/Configs/GameConfig/Datas/skill_effect.xlsx
+++ b/Client/Configs/GameConfig/Datas/skill_effect.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,43 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00000000"/>
-    </font>
-    <font>
-      <color rgb="007F6000"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8EEF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -76,20 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -164,46 +122,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>Codex</author>
-  </authors>
-  <commentList>
-    <comment ref="A1" authorId="0" shapeId="0">
-      <text>
-        <t>高级预留表：一个技能多个效果时再启用。当前原型主要使用 skill.xlsx 的 effectId。</t>
-      </text>
-    </comment>
-    <comment ref="B1" authorId="0" shapeId="0">
-      <text>
-        <t>技能效果关系ID。必须唯一。</t>
-      </text>
-    </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
-      <text>
-        <t>技能ID。指向 skill.xlsx。</t>
-      </text>
-    </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
-      <text>
-        <t>效果执行顺序。数值小的先执行。</t>
-      </text>
-    </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
-      <text>
-        <t>触发阶段。OnCast/OnHit/OnTick/OnExpire 等。当前示例用 OnHit。</t>
-      </text>
-    </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
-      <text>
-        <t>效果ID。指向 effect.xlsx。</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -495,187 +413,290 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>skillId</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>order</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>triggerPhase</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>effectId</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="48" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>技能效果关系ID。必须唯一。</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>技能ID。指向 skill.xlsx。</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>效果执行顺序。数值小的先执行。</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>触发阶段。OnCast/OnHit/OnTick/OnExpire 等。当前示例用 OnHit。</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>效果ID。指向 effect.xlsx。</t>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Relation id.</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Skill id.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Skill level.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Execution order.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Trigger phase.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Effect id.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n">
+      <c r="B5" t="n">
         <v>400101</v>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>100101</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
+      <c r="C5" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
         <is>
           <t>OnHit</t>
         </is>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="G5" t="n">
         <v>200101</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n">
+      <c r="B6" t="n">
         <v>400102</v>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>100102</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="C6" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>OnHit</t>
         </is>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="G6" t="n">
         <v>200102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>400201</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>200201</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>400202</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>200202</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>400301</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>OnCast</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>200301</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>400401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OnCast</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>200401</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/Client/Configs/GameConfig/Datas/skill_effect.xlsx
+++ b/Client/Configs/GameConfig/Datas/skill_effect.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,10 +566,10 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>400101</v>
+        <v>110100101</v>
       </c>
       <c r="C5" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="D5" t="n">
         <v>1</v>
@@ -583,21 +583,21 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>200101</v>
+        <v>210101</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>400102</v>
+        <v>110100201</v>
       </c>
       <c r="C6" t="n">
-        <v>1001</v>
+        <v>1101</v>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -605,18 +605,18 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>200102</v>
+        <v>210101</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="n">
-        <v>400201</v>
+        <v>110100301</v>
       </c>
       <c r="C7" t="n">
-        <v>1002</v>
+        <v>1101</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -627,21 +627,21 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>200201</v>
+        <v>210101</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>400202</v>
+        <v>110200101</v>
       </c>
       <c r="C8" t="n">
-        <v>1002</v>
+        <v>1102</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -649,51 +649,909 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>200202</v>
+        <v>210201</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>400301</v>
+        <v>110200102</v>
       </c>
       <c r="C9" t="n">
-        <v>1003</v>
+        <v>1102</v>
       </c>
       <c r="D9" t="n">
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>OnCast</t>
+          <t>OnHit</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>200301</v>
+        <v>210202</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>400401</v>
+        <v>110200201</v>
       </c>
       <c r="C10" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>210201</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>110200202</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>210202</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>110200301</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>210201</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>110200302</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>210202</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>110300101</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>210301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>110300102</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>210302</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>110300103</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>210303</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>110300201</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>210301</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>110300202</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>210302</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>110300203</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>210303</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>110300301</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>210301</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>110300302</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>210302</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>110300303</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>210303</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>120100101</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>220101</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>120100201</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D24" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>220101</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>120100301</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>220101</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>120200101</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>220201</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>120200102</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>220202</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>120200201</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D28" t="n">
+        <v>2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>220201</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>120200202</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D29" t="n">
+        <v>2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>220202</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>120200301</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>220201</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>120200302</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>220202</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>120300101</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>220301</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>120300102</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>220302</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>120300201</v>
+      </c>
+      <c r="C34" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>220301</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>120300202</v>
+      </c>
+      <c r="C35" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>220302</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>120300301</v>
+      </c>
+      <c r="C36" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>220301</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>120300302</v>
+      </c>
+      <c r="C37" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>220302</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>130100101</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>230101</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>130100201</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>230101</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="n">
+        <v>130100301</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>230101</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" t="n">
+        <v>130200101</v>
+      </c>
+      <c r="C41" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>230201</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="n">
+        <v>130200201</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>230201</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" t="n">
+        <v>130200301</v>
+      </c>
+      <c r="C43" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>230201</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>130300101</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>230301</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="n">
+        <v>130300201</v>
+      </c>
+      <c r="C45" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>230301</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>130300301</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>230301</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="B47" t="n">
+        <v>100400101</v>
+      </c>
+      <c r="C47" t="n">
         <v>1004</v>
       </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>OnCast</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>200401</v>
+      <c r="D47" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>200400</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="B48" t="n">
+        <v>100400201</v>
+      </c>
+      <c r="C48" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>200400</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" t="n">
+        <v>100400301</v>
+      </c>
+      <c r="C49" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>OnHit</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>200400</v>
       </c>
     </row>
   </sheetData>
